--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/6737-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/6737-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0988C68B-89B5-459A-ADD5-C494F5111372}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{852CC98E-0071-4AA2-9A7B-3B27F785B2A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{82F96E4D-69BA-47CD-AC22-63E11BEEE64D}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{7C3ED758-117D-4A10-B03E-F5CF56842FD0}"/>
   </bookViews>
   <sheets>
     <sheet name="6737-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1516,30 +1516,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DD9B396-F1BF-4752-BAC3-862BDDC19A2F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44A0A468-D7E6-4612-AC04-D56612EDA2EC}">
   <dimension ref="A1:X24"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11.125" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="6" width="7.125" customWidth="1"/>
-    <col min="7" max="9" width="6.75" customWidth="1"/>
-    <col min="10" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="14" width="7.125" customWidth="1"/>
-    <col min="15" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.75" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" customWidth="1"/>
+    <col min="6" max="6" width="6.109375" customWidth="1"/>
+    <col min="7" max="9" width="5.88671875" customWidth="1"/>
+    <col min="10" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="14" width="6.109375" customWidth="1"/>
+    <col min="15" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1573,7 +1573,7 @@
       <c r="W1" s="30"/>
       <c r="X1" s="22"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1609,7 +1609,7 @@
       <c r="W2" s="32"/>
       <c r="X2" s="33"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="X3" s="36"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1729,7 +1729,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="37">
         <v>2025</v>
       </c>
@@ -1801,7 +1801,7 @@
         <v>3.87</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="39"/>
       <c r="B6" s="40"/>
       <c r="C6" s="42"/>
@@ -1837,7 +1837,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>30</v>
       </c>
@@ -1911,7 +1911,7 @@
         <v>1.93</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="47">
         <v>2024</v>
       </c>
@@ -1983,7 +1983,7 @@
         <v>10.1</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="18" t="s">
         <v>30</v>
       </c>
@@ -2057,7 +2057,7 @@
         <v>4.8099999999999996</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="18" t="s">
         <v>30</v>
       </c>
@@ -2131,7 +2131,7 @@
         <v>5.29</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="49">
         <v>2023</v>
       </c>
@@ -2203,7 +2203,7 @@
         <v>5.56</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
         <v>30</v>
       </c>
@@ -2277,7 +2277,7 @@
         <v>3.17</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>30</v>
       </c>
@@ -2351,7 +2351,7 @@
         <v>2.38</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="47">
         <v>2022</v>
       </c>
@@ -2423,7 +2423,7 @@
         <v>6.66</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="18" t="s">
         <v>30</v>
       </c>
@@ -2497,7 +2497,7 @@
         <v>2.62</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="18" t="s">
         <v>30</v>
       </c>
@@ -2571,7 +2571,7 @@
         <v>4.03</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="49">
         <v>2021</v>
       </c>
@@ -2643,7 +2643,7 @@
         <v>7.45</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>30</v>
       </c>
@@ -2717,7 +2717,7 @@
         <v>4.03</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>30</v>
       </c>
@@ -2791,7 +2791,7 @@
         <v>3.41</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="47">
         <v>2020</v>
       </c>
@@ -2863,7 +2863,7 @@
         <v>7.85</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="18" t="s">
         <v>30</v>
       </c>
@@ -2937,7 +2937,7 @@
         <v>5.12</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="18" t="s">
         <v>30</v>
       </c>
@@ -3011,7 +3011,7 @@
         <v>2.73</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="49">
         <v>2019</v>
       </c>
@@ -3083,7 +3083,7 @@
         <v>6.78</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="47" t="s">
         <v>45</v>
       </c>
